--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0008.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0008.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chúng giấu kỹ thật... Let's see... Số dư tài khoản, nhật ký giao dịch... Ồ, tốt quá. Chúng chưa tiêu gì nhiều. Không phải đền bù nhiều từ tiền túi đâu.</t>
+          <t>Chúng giấu kỹ thật... Để xem nào... Số dư tài khoản, nhật ký giao dịch... Ồ, tốt quá. Chúng chưa tiêu gì nhiều. Không phải đền bù nhiều từ tiền túi đâu.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Này, ta biết là ngươi đấy, {PlayerName}! Đùa ta hả? Ta vừa kiểm tra, tín hiệu tốt mà. Còn đây, lịch sử trò chuyện của chúng ta đây này. Thôi, không nói nữa, ta có thông tin mới cho ngươi đây.</t>
+          <t>Này, tao biết là mày đấy, {PlayerName}! Đùa tao hả? Tao vừa kiểm tra, tín hiệu tốt mà. Còn đây, lịch sử trò chuyện của chúng ta đây này. Thôi, không nói nữa, tao có thông tin mới cho mày đây.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Hội Student thật sự đã đồng ý để ta lặng lẽ đóng tài khoản cũ và gộp dữ liệu vào cái mới. Bọn lừa đảo đó không xứng đáng gọi mình là "Kẻ Đào Mộ" đâu.</t>
+          <t>Hội Học sinh thật sự đã đồng ý để tao lặng lẽ đóng tài khoản cũ và gộp dữ liệu vào cái mới. Bọn lừa đảo đó không xứng đáng gọi mình là "Kẻ Đào Mộ" đâu.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>From now on, ta sẽ cho mọi người thấy một Scavenger thực thụ làm được gì. Sư phụ ta sẵn sàng hỗ trợ kỹ thuật. Joss sẽ là khách hàng đầu tiên của chúng ta. Dù hắn chưa biết điều đó.</t>
+          <t>Từ giờ trở đi, tao sẽ cho mọi người thấy một Scavenger thực thụ làm được gì. Sư phụ tao sẵn sàng hỗ trợ kỹ thuật. Joss sẽ là khách hàng đầu tiên của chúng ta. Dù hắn chưa biết điều đó.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Nhưng sau tất cả những gì chúng ta đã trải qua cùng nhau… ta lại tìm thấy ngọn lửa ấy. Ngọn lửa mà ta đã mang theo từ ngày đầu bước chân vào Startorch Academy. Ngọn lửa chiến thắng Void Storm!</t>
+          <t>Nhưng sau tất cả những gì chúng ta đã trải qua cùng nhau… ta lại tìm thấy ngọn lửa ấy. Ngọn lửa mà ta đã mang theo từ ngày đầu bước chân vào Học viện Startorch. Ngọn lửa chiến thắng Bão Hư Không!</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nghe này, ta đâu phải đội cứu hộ đâu. Ta chỉ thấy tin nhắn WavesLine của ngươi nên đến xem ngươi ổn không thôi. Ngươi làm cái gì ở đây mà cần "bí mật" đến thế?</t>
+          <t>Nghe này, tao đâu phải đội cứu hộ đâu. Tao chỉ thấy tin nhắn WavesLine của mày nên đến xem mày ổn không thôi. Mày làm cái gì ở đây mà cần "bí mật" đến thế?</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Còn về mật mã… ta chọn "7195, one Kronaclaw." Còn về "vật phẩm thất lạc," chúng ta sẽ yêu cầu một đèn hiệu định vị. Họ đã làm giả một cái cho ta trước đây, nên sẽ nhanh thôi. Phần còn lại là tùy các ngươi!</t>
+          <t>Còn về mật mã… ta chọn "7195, một Kronaclaw." Còn về "vật phẩm thất lạc," chúng ta sẽ yêu cầu một đèn hiệu định vị. Họ đã làm giả một cái cho ta trước đây, nên sẽ nhanh thôi. Phần còn lại là tùy các ngươi!</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>["Tảng đá khắc họa hình một chú Fluffguin, một Kronapuff và một Toskr Lemming. Chúng quây quần vui vẻ bên một cô bé Roya đang khắc tượng bằng con dao nhỏ.]
-[Dù chỉ là những Dodget khắc đơn sơ, nhưng chi tiết lại rất rõ ràng: Toskr Lemming đeo một thiết bị nghe giống như tai nghe, Fluffguin ôm bát cá, còn Kronapuff ngậm một bông hoa trong miệng.]
+[Dù chỉ là những nét khắc đơn sơ, nhưng chi tiết lại rất rõ ràng: Toskr Lemming đeo một thiết bị nghe giống như tai nghe, Fluffguin ôm bát cá, còn Kronapuff ngậm một bông hoa trong miệng.]
 Gửi những người bạn thân nhất của ta: Fenrir, người yêu thích khiêu vũ. Dallas, người mê ăn cá. Và Bori, người yêu hoa.
 Ta khắc các ngươi lên tảng đá này, để chúng ta mãi mãi bên nhau. Mãi mãi.</t>
         </is>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu Tập thể Spacetrek - Report Thực địa (Lưu trữ)
-Chủ đề Nghiên cứu: Đặc tính Động lực của Discord "Inferno Rider" và Phương tiện của nó
+          <t>Viện Nghiên cứu Tập thể Spacetrek - Báo cáo Thực địa (Lưu trữ)
+Chủ đề Nghiên cứu: Đặc tính Động lực của Tacet Discord "Inferno Rider" và Phương tiện của nó
 Địa điểm Nghiên cứu: Huanglong — Thành phố Cảng Guixu
 Dự án Liên quan: Nghiên cứu &amp; Phát triển Lặp lại Mẫu Xe Máy Thám hiểm Nguyên mẫu
 I. Bối cảnh
-Một Discord mạnh mẽ, được định danh là "Inferno Rider", đã được quan sát gần Thành phố Cảng Guixu ở Huanglong. Phương tiện mà nó sử dụng vận hành với độ ổn định đáng kinh ngạc trong môi trường hậu-Lament. Thiết kế cấu trúc và mô hình di chuyển của nó dự kiến sẽ cung cấp những điểm tham chiếu quan trọng cho việc phát triển mẫu xe máy thám hiểm nguyên mẫu của chúng ta.
+Một Tacet Discord mạnh mẽ, được định danh là "Inferno Rider", đã được quan sát gần Thành phố Cảng Guixu ở Huanglong. Phương tiện mà nó sử dụng vận hành với độ ổn định đáng kinh ngạc trong môi trường hậu-Lament. Thiết kế cấu trúc và mô hình di chuyển của nó dự kiến sẽ cung cấp những điểm tham chiếu quan trọng cho việc phát triển mẫu xe máy thám hiểm nguyên mẫu của chúng ta.
 II. Ghi chép Thực địa
 Địa điểm: Thành phố Cảng Guixu — Tàn tích Cầu vượt
 Bằng cách triển khai các cảm biến để thu thập dữ liệu động học, chúng tôi đã xác định rằng "Inferno Rider" hoạt động vượt trội hơn mức trung bình ở các khía cạnh sau:
@@ -2629,7 +2629,7 @@
 ……………………
 &lt;b&gt;Ghi chú viết tay của Nhà nghiên cứu:&lt;/b&gt;
 &lt;b&gt;Nguyên mẫu đã hoàn thành. Tôi không ngờ công nghệ cũ từ quê hương mình bao năm trước lại có thể hồi sinh trong một chiếc xe máy thám hiểm.&lt;/b&gt;
-&lt;b&gt;Ngay cả bây giờ, cái tên "Inferno Rider" vẫn khiến người ta khiếp sợ. Tôi không thể xóa đi bóng tối mà Discord ấy đã gieo rắc, cũng không thể thực sự mang lại sự an nghỉ cho những linh hồn đã khuất từ lâu. Ít nhất, nguyên mẫu này chứng minh rằng tổ tiên chúng ta đã để lại không chỉ nỗi đau và sự kinh hoàng.&lt;/b&gt;
+&lt;b&gt;Ngay cả bây giờ, cái tên "Inferno Rider" vẫn khiến người ta khiếp sợ. Tôi không thể xóa đi bóng tối mà Tacet Discord ấy đã gieo rắc, cũng không thể thực sự mang lại sự an nghỉ cho những linh hồn đã khuất từ lâu. Ít nhất, nguyên mẫu này chứng minh rằng tổ tiên chúng ta đã để lại không chỉ nỗi đau và sự kinh hoàng.&lt;/b&gt;
 &lt;b&gt;Họ còn có cả hy vọng về tương lai.&lt;/b&gt;
 &lt;b&gt;Chiếc xe này sẽ mang theo ý chí của họ, bảo vệ con đường cho những ai dám khám phá.&lt;/b&gt;</t>
         </is>
@@ -2970,13 +2970,13 @@
 Đơn vị cung cấp: Cửa hàng Mahe
 Mặt hàng:
 Ớt khô: 10 thùng
-Vinegar: 10 thùng
+Giấm: 10 thùng
 Gia vị lẩu: 10 thùng
 Dầu mè cao cấp: 10 thùng
-Rice: 50 bao
+Gạo: 50 bao
 Trứng: 50 thùng
-Address giao hàng: Ký túc xá học viên, Startorch Academy
-&lt;b&gt;Liên kết cùng Lollo Logistics, Cửa hàng Mahe tự hào cam kết giao hàng trong vòng 30 ngày kể từ khi đặt. Chúng tôi cung cấp đa dạng các loại đồ ăn vặt, gia vị và dụng cụ bếp đặc sản Huanglong—lý tưởng cho học viên Startorch Academy! Đặt hàng ngay khi còn hàng. Buy càng nhiều, tiết kiệm càng nhiều.&lt;/b&gt;</t>
+Địa chỉ giao hàng: Ký túc xá học viên, Học viện Startorch
+&lt;b&gt;Liên kết cùng Lollo Logistics, Cửa hàng Mahe tự hào cam kết giao hàng trong vòng 30 ngày kể từ khi đặt. Chúng tôi cung cấp đa dạng các loại đồ ăn vặt, gia vị và dụng cụ bếp đặc sản Huanglong—lý tưởng cho học viên Học viện Startorch! Đặt hàng ngay khi còn hàng. Mua càng nhiều, tiết kiệm càng nhiều.&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Welcome... Ước gì ta có thể chào đón nồng nhiệt hơn, nhưng Patty đang gặp chút trục trặc kỹ thuật và chúng ta không thể tiếp nhận điều ước mới tại Moontree Lodge cho đến khi ta giải quyết xong vấn đề.</t>
+          <t>Chào mừng... Ước gì ta có thể chào đón nồng nhiệt hơn, nhưng Patty đang gặp chút trục trặc kỹ thuật và chúng ta không thể tiếp nhận điều ước mới tại Moontree Lodge cho đến khi ta giải quyết xong vấn đề.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ngoài ra... dù chỉ trong thoáng chốc, tôi đã phát hiện sự dao động tần số bất thường sau khi kết nối Patty với Terminal của mình. Về lý thuyết, dữ liệu của robot không thể tạo ra những dao động như vậy.</t>
+          <t>Ngoài ra... dù chỉ trong thoáng chốc, tôi đã phát hiện sự dao động tần số bất thường sau khi kết nối Patty với Thiết bị đầu cuối của mình. Về lý thuyết, dữ liệu của robot không thể tạo ra những dao động như vậy.</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tuy nhiên, trong quá trình thử nghiệm gần đây, ta phát hiện ra những đoạn mã bất thường trong cơ sở dữ liệu của Patty. Like một loại virus, chúng lan rộng chóng mặt với mỗi điều ước được thêm vào.</t>
+          <t>Tuy nhiên, trong quá trình thử nghiệm gần đây, ta phát hiện ra những đoạn mã bất thường trong cơ sở dữ liệu của Patty. Giống như một loại virus, chúng lan rộng chóng mặt với mỗi điều ước được thêm vào.</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chắc hắn cũng đã nhận ra cậu là ai rồi. Thế nên mới kiếm cớ chuồn đi vội vàng. Hmm... vẫn thế, trốn tránh vấn đề như mọi khi.</t>
+          <t>Chắc hắn cũng đã nhận ra cậu là ai rồi. Thế nên mới kiếm cớ chuồn đi vội vàng. Hừm... vẫn thế, trốn tránh vấn đề như mọi khi.</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>À, đó là hậu quả của một tai nạn trong thí nghiệm về Echoes cách đây một thời gian. Không quá nghiêm trọng, nhưng vẫn để lại vài di chứng. Từ đó đến giờ, tớ không thể điều khiển bất kỳ thiết bị chính xác nào nữa.</t>
+          <t>À, đó là hậu quả của một tai nạn trong thí nghiệm về Echo cách đây một thời gian. Không quá nghiêm trọng, nhưng vẫn để lại vài di chứng. Từ đó đến giờ, tớ không thể điều khiển bất kỳ thiết bị chính xác nào nữa.</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Xiang-LEE và {PlayerName} đang nghiên cứu về Echoes nhưng gặp bế tắc. Họ nghe nói ông Shifan là chuyên gia trong lĩnh vực này nên đến nhờ giúp đỡ.</t>
+          <t>Hương-LY và {PlayerName} đang nghiên cứu về Echo nhưng gặp bế tắc. Họ nghe nói ông Shifan là chuyên gia trong lĩnh vực này nên đến nhờ giúp đỡ.</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Chúng tôi đã hứa sẽ đẩy xa giới hạn nghiên cứu Echo. Tôi luôn tin rằng chúng ta có thể đạt được thành tựu đột phá, thậm chí chạm tới bản chất của Lời Than qua nghiên cứu. Nhưng vì sự bất cẩn của tôi, cậu ấy đã mất đi cơ hội bước qua cánh cửa đó mãi mãi.</t>
+          <t>Chúng tôi đã hứa sẽ đẩy xa giới hạn nghiên cứu Tiếng Vọng. Tôi luôn tin rằng chúng ta có thể đạt được thành tựu đột phá, thậm chí chạm tới bản chất của Lời Than qua nghiên cứu. Nhưng vì sự bất cẩn của tôi, cậu ấy đã mất đi cơ hội bước qua cánh cửa đó mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Bà Hạc Doanh, bà có muốn cùng chúng tôi ghé qua Lữ Quán không? Taoyuan Vale đang chuẩn bị cho Hội Chợ Trăng, bầu không khí rất náo nhiệt. Đi dạo một chút có khi tâm trạng bà sẽ khá hơn đấy.</t>
+          <t>Bà Hạc Doanh, bà có muốn cùng chúng tôi ghé qua Lữ Quán không? Thung Lũng Đào Nguyên đang chuẩn bị cho Hội Chợ Trăng, bầu không khí rất náo nhiệt. Đi dạo một chút có khi tâm trạng bà sẽ khá hơn đấy.</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Cô ấy mong rằng ai nhìn thấy chiếc quạt này cũng sẽ cảm nhận được không khí rộn ràng của Moon-Chasing Festival, và nhớ rằng tất cả niềm vui ấy đều nhờ công của các Hộ Vệ Dũng Cảm.</t>
+          <t>Cô ấy mong rằng ai nhìn thấy chiếc quạt này cũng sẽ cảm nhận được không khí rộn ràng của Lễ Hội Đuổi Trăng, và nhớ rằng tất cả niềm vui ấy đều nhờ công của các Hộ Vệ Dũng Cảm.</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>...À, mình hiểu rồi, Momo... lại định lừa mình nữa à... Trong "Giải Cứu Deep Sea", Ranger Lửa bị rơi vào bẫy của kẻ xấu và bị đánh tơi tả ngay từ đầu đấy!</t>
+          <t>...À, mình hiểu rồi, Momo... lại định lừa mình nữa à... Trong "Giải Cứu Biển Sâu", Ranger Lửa bị rơi vào bẫy của kẻ xấu và bị đánh tơi tả ngay từ đầu đấy!</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Và đừng quên Moonlit Fair nữa! Đây là sự kiện độc quyền của Jinzhou, chỉ diễn ra vào đêm hội. Có đủ thứ để ăn, uống, chơi và ngắm đấy!</t>
+          <t>Và đừng quên Hội Chợ Ánh Trăng nữa! Đây là sự kiện độc quyền của Jinzhou, chỉ diễn ra vào đêm hội. Có đủ thứ để ăn, uống, chơi và ngắm đấy!</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Tôi chỉ đưa ra vài ý tưởng thôi, nhưng rất vui vì đã giúp được gì đó. Lúc đó tôi đang hỗ trợ Ministry of Development sửa một tháp giám sát bị hỏng. Khi quay lại phòng thí nghiệm thì cậu đã đi rồi...</t>
+          <t>Tôi chỉ đưa ra vài ý tưởng thôi, nhưng rất vui vì đã giúp được gì đó. Lúc đó tôi đang hỗ trợ Bộ Phát Triển sửa một tháp giám sát bị hỏng. Khi quay lại phòng thí nghiệm thì cậu đã đi rồi...</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Khi đến Cây Wish, cậu gặp chủ nhân của con robot, Xiangli Yao, Trưởng Điều Tra viên của Huaxu Academy. Xiangli Yao giải thích rằng robot của ông, "Patty", đang gặp trục trặc, và những lời nói vô nghĩa của nó khiến cậu nhận ra Xiangli Yao có lẽ chính là anh hùng thầm lặng mà Chixia đã nhắc tới. Xiangli nhờ cậu giữ bí mật chuyện đó. Sau khi biết cậu đến để ước nguyện, ông đề nghị ghé qua Wishing Stall để trò chuyện.</t>
+          <t>Khi đến Cây Ước Nguyện, cậu gặp chủ nhân của con robot, Xiangli Yao, Trưởng Điều Tra viên của Học viện Huaxu. Xiangli Yao giải thích rằng robot của ông, "Patty", đang gặp trục trặc, và những lời nói vô nghĩa của nó khiến cậu nhận ra Xiangli Yao có lẽ chính là anh hùng thầm lặng mà Chixia đã nhắc tới. Xiangli nhờ cậu giữ bí mật chuyện đó. Sau khi biết cậu đến để ước nguyện, ông đề nghị ghé qua Gian Hàng Ước Nguyện để trò chuyện.</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Tương Lị Yao tiết lộ rằng Patty đang gặp một số trục trặc kỹ thuật, có lẽ do bốn điều ước không thể đọc được gây ra. Để đảm bảo mọi người đều có thể tận hưởng lễ hội, cậu đề nghị giúp Tương Lị Yao giải quyết vấn đề.</t>
+          <t>Tương Lị Dao tiết lộ rằng Patty đang gặp một số trục trặc kỹ thuật, có lẽ do bốn điều ước không thể đọc được gây ra. Để đảm bảo mọi người đều có thể tận hưởng lễ hội, cậu đề nghị giúp Tương Lị Dao giải quyết vấn đề.</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Trong lúc trò chuyện, bà Heying kể về lời hứa bà đã dành cho con trai quá cố của mình, Xiuyuan. Để xoa dịu nỗi đau của bà, cậu đưa bà đến Taoyuan Vale để trải nghiệm niềm vui của lễ hội.</t>
+          <t>Trong lúc trò chuyện, bà Heying kể về lời hứa bà đã dành cho con trai quá cố của mình, Xiuyuan. Để xoa dịu nỗi đau của bà, cậu đưa bà đến Thung Lũng Đào Nguyên để trải nghiệm niềm vui của lễ hội.</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bạn trở lại Quầy Ước Nguyện và thảo luận với Xiangli Yao về những ứng cử viên tiềm năng cho vị anh hùng của Mahn. Khi cân nhắc các lựa chọn, Xiangli Yao đề xuất rằng chính bạn là lựa chọn tốt nhất. Để củng cố ý tưởng này, Xiangli điều chỉnh Terminal của bạn để ghi lại cuộc sống hàng ngày, dự định dùng làm tài liệu tham khảo cho Mahn.</t>
+          <t>Bạn trở lại Quầy Ước Nguyện và thảo luận với Xiangli Yao về những ứng cử viên tiềm năng cho vị anh hùng của Mahn. Khi cân nhắc các lựa chọn, Xiangli Yao đề xuất rằng chính bạn là lựa chọn tốt nhất. Để củng cố ý tưởng này, Xiangli điều chỉnh Thiết bị đầu cuối của bạn để ghi lại cuộc sống hàng ngày, dự định dùng làm tài liệu tham khảo cho Mahn.</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Dưới gốc Cây Wish, Xiangli Yao cho cậu biết Patty đã trở thành cánh cổng dẫn vào một Sonoro Sphere, và dữ liệu bất thường có lẽ đang ẩn náu trong điều ước thứ tư. Để đảm bảo Moonlit Fair diễn ra suôn sẻ, cậu, Abby và Xiangli Yao quyết định bước vào và điều tra Sonoro này.</t>
+          <t>Dưới gốc Cây Ước Nguyện, Xiangli Yao cho cậu biết Patty đã trở thành cánh cổng dẫn vào một Sonoro Sphere, và dữ liệu bất thường có lẽ đang ẩn náu trong điều ước thứ tư. Để đảm bảo Hội Chợ Ánh Trăng diễn ra suôn sẻ, cậu, Abby và Xiangli Yao quyết định bước vào và điều tra Sonoro này.</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Chúng tôi vẫn đang tìm cách tái tạo nguyên mẫu của cậu. Nhưng lý thuyết "Pascar Spectrum" đã được thế giới công nhận và đang thúc đẩy nghiên cứu về Tacet Field.</t>
+          <t>Chúng tôi vẫn đang tìm cách tái tạo nguyên mẫu của cậu. Nhưng lý thuyết "Pascar Spectrum" đã được thế giới công nhận và đang thúc đẩy nghiên cứu về Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Xem thử quanh đây đã. Ta chẳng biết mấy về ngọn hải đăng ở Reyes này, nhưng trước khi trời tối, con cá biển kia sẽ phải treo trên mũi thuyền của ta, nghe chưa!</t>
+          <t>Xem thử quanh đây đã. Tao chẳng biết mấy về ngọn hải đăng ở Reyes này, nhưng trước khi trời tối, con cá biển kia sẽ phải treo trên mũi thuyền của tao, nghe chưa!</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tớ vẫn nhớ lần trước cậu lật thuyền của chúng ta đấy. Nhưng thôi, vì cậu vừa cứu chúng ta nên tớ sẽ bỏ qua! Hmph... Like câu nói ở Jinzhou xưa, đại loại là "Người lớn không chấp những chuyện nhỏ nhặt!"</t>
+          <t>Tớ vẫn nhớ lần trước cậu lật thuyền của chúng ta đấy. Nhưng thôi, vì cậu vừa cứu chúng ta nên tớ sẽ bỏ qua! Hừ... Giống như câu nói ở Jinzhou xưa, đại loại là "Người lớn không chấp những chuyện nhỏ nhặt!"</t>
         </is>
       </c>
     </row>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mấy tuần nay ông ta hơi mất trí rồi. Người ta bảo từ khi thoáng thấy Tidebreaker, ông ta mới bắt đầu hành động kỳ cục. Dù sao, bảo ông ta là ta gửi cậu đến nhé.</t>
+          <t>Mấy tuần nay ông ta hơi mất trí rồi. Người ta bảo từ khi thoáng thấy Tidebreaker, ông ta mới bắt đầu hành động kỳ cục. Dù sao, bảo ông ta là tao gửi cậu đến nhé.</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tại Cathedral of Mercury, Cristoforo tiết lộ kế hoạch của Fenrico. Trong cuộc đối đầu, Fenrico nghi ngờ rằng Cristoforo chính là người đã bí mật dẫn dắt Hội Thi Sĩ suốt bao năm qua.</t>
+          <t>Tại Nhà Thờ Mercury, Cristoforo tiết lộ kế hoạch của Fenrico. Trong cuộc đối đầu, Fenrico nghi ngờ rằng Cristoforo chính là người đã bí mật dẫn dắt Hội Thi Sĩ suốt bao năm qua.</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tôi xin lỗi, Ngài Tu Sĩ. Tôi đang cố hết sức hợp tác. Xin đừng hiểu im lặng của tôi là chống đối. It's just... căn phòng này lạnh quá, tôi bị cảm lạnh rồi. Khó mà nói chuyện được.</t>
+          <t>Tôi xin lỗi, Ngài Tu Sĩ. Tôi đang cố hết sức hợp tác. Xin đừng hiểu im lặng của tôi là chống đối. Chỉ là... căn phòng này lạnh quá, tôi bị cảm lạnh rồi. Khó mà nói chuyện được.</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Khi bạn chạm vào giai điệu Remnant của Faroll, sự thật dần sáng tỏ: hắn đã nhìn thấy số phận này từ trước. Lý do chúng bị bắt không phải vì tội báng bổ, mà là vì đã khám phá ra bộ mặt thật của Sentinel.</t>
+          <t>Khi bạn chạm vào giai điệu Tàn Tích của Faroll, sự thật dần sáng tỏ: hắn đã nhìn thấy số phận này từ trước. Lý do chúng bị bắt không phải vì tội báng bổ, mà là vì đã khám phá ra bộ mặt thật của Sentinel.</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Nhiệm vụ đã nộp rồi, dù ta có lo lắng đến mấy cũng chẳng thay đổi được những gì đã xảy ra hay sắp xảy đến. Nhưng mà... ta cứ mãi nghĩ về nó, không ngừng nghĩ về nó.</t>
+          <t>Nhiệm vụ đã nộp rồi, dù tao có lo lắng đến mấy cũng chẳng thay đổi được những gì đã xảy ra hay sắp xảy đến. Nhưng mà... tao cứ mãi nghĩ về nó, không ngừng nghĩ về nó.</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tuyến đường này sẽ một lần nữa đưa nguồn cung ứng và nhân tài ổn định đến Spacetrek Observatory. Các nghiên cứu thực địa về Giant's Gaze của Học Viện Startorch từ lâu bị đình trệ cũng sẽ được tiếp tục nhờ kết nối quan trọng này.</t>
+          <t>Tuyến đường này sẽ một lần nữa đưa nguồn cung ứng và nhân tài ổn định đến Đài Thiên Văn Spacetrek. Các nghiên cứu thực địa về Giant's Gaze của Học Viện Startorch từ lâu bị đình trệ cũng sẽ được tiếp tục nhờ kết nối quan trọng này.</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Đây là khóa huấn luyện chiến đấu ảo do giảng viên, sinh viên và kỹ sư của Học viện Rabelle cùng phát triển. Nó dùng để test khả năng chiến đấu của sinh viên trong môi trường khắc nghiệt.</t>
+          <t>Đây là khóa huấn luyện chiến đấu ảo do giảng viên, sinh viên và kỹ sư của Học viện Rabelle cùng phát triển. Nó dùng để kiểm tra khả năng chiến đấu của sinh viên trong môi trường khắc nghiệt.</t>
         </is>
       </c>
     </row>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Ta đã đến nhiều giếng ước rồi, nên ta biết mỗi nơi lại có phong tục ước nguyện riêng. Chính vì thế, nếu không làm đúng thủ tục, ước nguyện của ngươi sẽ chẳng bao giờ thành hiện thực đâu!</t>
+          <t>Tao đã đến nhiều giếng ước rồi, nên tao biết mỗi nơi lại có phong tục ước nguyện riêng. Chính vì thế, nếu không làm đúng thủ tục, ước nguyện của mày sẽ chẳng bao giờ thành hiện thực đâu!</t>
         </is>
       </c>
     </row>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Lần trước, cậu bảo chưa ngắm hết cảnh bên trái. Rồi lần khác, cậu lại bảo không chụp được ảnh ta với đấu trường làm nền. Lần này thì sao?</t>
+          <t>Lần trước, cậu bảo chưa ngắm hết cảnh bên trái. Rồi lần khác, cậu lại bảo không chụp được ảnh tao với đấu trường làm nền. Lần này thì sao?</t>
         </is>
       </c>
     </row>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>High Tide. Chính là High Tide. Đúng, chủ đề nóng hổi của giờ phút này. Lý do duy nhất khiến nhiệt huyết đến thành phố xem Agon giảm xuống mức thấp kỷ lục. Đồng nghĩa với doanh số bán đồ lưu niệm của chúng ta cũng lao dốc!</t>
+          <t>Triều Cường. Chính là Triều Cường. Đúng, chủ đề nóng hổi của giờ phút này. Lý do duy nhất khiến nhiệt huyết đến thành phố xem Agon giảm xuống mức thấp kỷ lục. Đồng nghĩa với doanh số bán đồ lưu niệm của chúng ta cũng lao dốc!</t>
         </is>
       </c>
     </row>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>How've you been? Tuần này tớ tham gia trận tập đấu nữa nhưng lại thua ở vòng chung kết. Tớ sẽ đăng ký trận thật khi nào thắng liên tiếp ba vòng.</t>
+          <t>Dạo này cậu sao rồi? Tuần này tớ tham gia trận tập đấu nữa nhưng lại thua ở vòng chung kết. Tớ sẽ đăng ký trận thật khi nào thắng liên tiếp ba vòng.</t>
         </is>
       </c>
     </row>
@@ -18837,7 +18837,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Bạn're not alone. Cách cô ấy khiến mọi người hứng khởi với Agon thật khác lạ. Cô ấy còn đích thân đến xem các trận đấu, thậm chí còn chủ trì cả giải vô địch nữa!</t>
+          <t>Cậu không cô đơn đâu. Cách cô ấy khiến mọi người hứng khởi với Agon thật khác lạ. Cô ấy còn đích thân đến xem các trận đấu, thậm chí còn chủ trì cả giải vô địch nữa!</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Thưa Master Olet, nhà tắm công cộng dành cho thường dân chỉ mở cửa cho nam khách sau bốn giờ chiều. Trước đó, nơi này chỉ dành riêng cho nữ khách mà thôi.</t>
+          <t>Thưa Sư phụ Olet, nhà tắm công cộng dành cho thường dân chỉ mở cửa cho nam khách sau bốn giờ chiều. Trước đó, nơi này chỉ dành riêng cho nữ khách mà thôi.</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Tuổi còn nhỏ mà cậu ăn nói khéo léo thế, lại còn có cái nhìn sâu sắc nữa… Interesting. Này, lần sau cậu dẫn ta đi thăm lại nơi này nhé? Ta còn muốn tự mình khám phá nhiều thứ lắm.</t>
+          <t>Tuổi còn nhỏ mà cậu ăn nói khéo léo thế, lại còn có cái nhìn sâu sắc nữa… Thú vị thật. Này, lần sau cậu dẫn ta đi thăm lại nơi này nhé? Ta còn muốn tự mình khám phá nhiều thứ lắm.</t>
         </is>
       </c>
     </row>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Julius. Male. Dân thường Septimont. Sinh ra trên con tàu Fool's Sail trôi dạt đến Septimont cách đây hai mươi ba năm. Kết hôn với một phụ nữ dân thường khác ở Hạ Thành ba năm trước, từ đó lấy tên là Julius. Họ có một đứa con trai, mắc chứng suy giảm nhận thức nghi do Hắc Triều gây ra.</t>
+          <t>Julius. Nam. Dân thường Septimont. Sinh ra trên con tàu Fool's Sail trôi dạt đến Septimont cách đây hai mươi ba năm. Kết hôn với một phụ nữ dân thường khác ở Hạ Thành ba năm trước, từ đó lấy tên là Julius. Họ có một đứa con trai, mắc chứng suy giảm nhận thức nghi do Hắc Triều gây ra.</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Tạo thêm lựa chọn Dodge đòn, đồng thời cho phép bạn chộp lấy vũ khí của đối thủ bằng khiên vai. Và nếu tình thế cấp bách, bạn có thể tận dụng đà đó lao thẳng vào họ để thu hẹp khoảng cách...</t>
+          <t>Tạo thêm lựa chọn né đòn, đồng thời cho phép bạn chộp lấy vũ khí của đối thủ bằng khiên vai. Và nếu tình thế cấp bách, bạn có thể tận dụng đà đó lao thẳng vào họ để thu hẹp khoảng cách...</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Chúng nó kỳ quái như ngươi nói thật à? Ngươi bảo ta không biết một tên Đấu Sĩ nào muốn bán nhà tắm riêng à? Thôi nào, giới thiệu cho ta một đứa đi, ta sẽ trả hậu hĩnh cho.</t>
+          <t>Chúng nó kỳ quái như mày nói thật à? Mày bảo tao không biết một tên Đấu Sĩ nào muốn bán nhà tắm riêng à? Thôi nào, giới thiệu cho tao một đứa đi, tao sẽ trả hậu hĩnh cho.</t>
         </is>
       </c>
     </row>
@@ -21892,7 +21892,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Well... khác với các hiệp hội chuyên nghiệp khác ở Septimont đòi hỏi lý lịch và bộ kỹ năng cụ thể để nhận học việc, nhà tắm công cộng có cách tuyển dụng riêng. Cậu sẽ phải trải qua một buổi phỏng vấn và kiểm tra lý lịch.</t>
+          <t>Thì... khác với các hiệp hội chuyên nghiệp khác ở Septimont đòi hỏi lý lịch và bộ kỹ năng cụ thể để nhận học việc, nhà tắm công cộng có cách tuyển dụng riêng. Cậu sẽ phải trải qua một buổi phỏng vấn và kiểm tra lý lịch.</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Chúng ta đã phát hiện kẻ buôn lậu đang vận chuyển các Thiết bị đầu cuối đã bị chỉnh sửa, loại có thể qua mặt hệ thống an ninh giải đấu và cho phép sử dụng Echoes bất hợp pháp trong Agon.</t>
+          <t>Chúng ta đã phát hiện kẻ buôn lậu đang vận chuyển các Thiết bị đầu cuối đã bị chỉnh sửa, loại có thể qua mặt hệ thống an ninh giải đấu và cho phép sử dụng Echo bất hợp pháp trong Agon.</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Một lần nữa, tôi xin gửi tới các vị lời cảm ơn chân thành nhất. Từ nay về sau, chúng tôi sẽ tuyển thêm nhiều Resonators hơn nữa cho công việc, và cùng nhau bảo vệ các cổng dẫn tới Septimont!</t>
+          <t>Một lần nữa, tôi xin gửi tới các vị lời cảm ơn chân thành nhất. Từ nay về sau, chúng tôi sẽ tuyển thêm nhiều Resonator hơn nữa cho công việc, và cùng nhau bảo vệ các cổng dẫn tới Septimont!</t>
         </is>
       </c>
     </row>
@@ -22412,7 +22412,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi. Không phải cậu là thiên tài sống à? Này, thiên tài đấy. Nhìn xem ai vừa lỡ chuyến phà cuối về Ragunna nào. Đừng có mà đến cầu cứu ta nếu tối nay không có chỗ ngủ nhé.</t>
+          <t>Được rồi, được rồi. Không phải cậu là thiên tài sống à? Này, thiên tài đấy. Nhìn xem ai vừa lỡ chuyến phà cuối về Ragunna nào. Đừng có mà đến cầu cứu tao nếu tối nay không có chỗ ngủ nhé.</t>
         </is>
       </c>
     </row>
@@ -22477,7 +22477,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đúng rồi, hồi đó ta gầy như que củi ấy. Nhưng từ khi xem các trận đấu Gladiator ở Septimont, ta bắt đầu mê mẩn lịch tập luyện của bọn Gladiator luôn.</t>
+          <t>Đúng rồi, hồi đó tao gầy như que củi ấy. Nhưng từ khi xem các trận đấu Gladiator ở Septimont, tao bắt đầu mê mẩn lịch tập luyện của bọn Gladiator luôn.</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Very well. Tổ tiên chúng ta đã đặt chân lên mảnh đất này ngay tại đây. Họ lập tức được chào đón bởi Titanbone Expanse hùng vĩ và nhận ra vùng đất này sở hữu những phẩm chất xứng tầm với họ.</t>
+          <t>Được thôi. Tổ tiên chúng ta đã đặt chân lên mảnh đất này ngay tại đây. Họ lập tức được chào đón bởi Titanbone Expanse hùng vĩ và nhận ra vùng đất này sở hữu những phẩm chất xứng tầm với họ.</t>
         </is>
       </c>
     </row>
@@ -22997,7 +22997,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Một lần nữa, tôi xin gửi tới các vị lời cảm ơn chân thành nhất. Từ nay về sau, chúng tôi sẽ tuyển thêm nhiều Resonators hơn nữa cho công việc, và cùng nhau bảo vệ các cổng dẫn tới Septimont!</t>
+          <t>Một lần nữa, tôi xin gửi tới các vị lời cảm ơn chân thành nhất. Từ nay về sau, chúng tôi sẽ tuyển thêm nhiều Resonator hơn nữa cho công việc, và cùng nhau bảo vệ các cổng dẫn tới Septimont!</t>
         </is>
       </c>
     </row>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>À, đúng rồi. Of course. Chúng ta đã nhận được rất nhiều báo cáo về vấn đề này. Nhưng người đó đã được thẩm vấn và thả ra. Nếu thực sự có vấn đề với hàng hóa hắn vận chuyển, thì đây không phải chuyện nhỏ đâu.</t>
+          <t>À, đúng rồi. Tất nhiên rồi. Chúng ta đã nhận được rất nhiều báo cáo về vấn đề này. Nhưng người đó đã được thẩm vấn và thả ra. Nếu thực sự có vấn đề với hàng hóa hắn vận chuyển, thì đây không phải chuyện nhỏ đâu.</t>
         </is>
       </c>
     </row>
@@ -28002,7 +28002,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Bọn Lưu Đày à, chúng đâu thèm quan tâm nhà ngươi ở đâu. Chúng chỉ muốn chặn tín hiệu liên lạc của ngươi và cướp động cơ lẫn mô-đun năng lượng khi ngươi không đề phòng thôi…</t>
+          <t>Bọn Lưu Đày à, chúng đâu thèm quan tâm nhà mày ở đâu. Chúng chỉ muốn chặn tín hiệu liên lạc của mày và cướp động cơ lẫn mô-đun năng lượng khi mày không đề phòng thôi…</t>
         </is>
       </c>
     </row>
@@ -28197,7 +28197,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đây là lãnh địa của ta! Ta nói gì thì nghe nấy. À, ngươi không muốn biết thằng "điều hành" tự phong kia đã ra sao khi dám chống lại ta lần trước đâu...</t>
+          <t>Đây là lãnh địa của tao! Tao nói gì thì nghe nấy. À, mày không muốn biết thằng "điều hành" tự phong kia đã ra sao khi dám chống lại tao lần trước đâu...</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Ta hứa sẽ luôn sát cánh bên cạnh cậu, không chút dao động khi cậu bắt đầu hành trình, và khi cậu trở nên mạnh mẽ hơn, ta sẽ trao cho cậu thêm nhiều chìa khóa để giải mã những bí ẩn phía trước.</t>
+          <t>Tao hứa sẽ luôn sát cánh bên cạnh cậu, không chút dao động khi cậu bắt đầu hành trình, và khi cậu trở nên mạnh mẽ hơn, tao sẽ trao cho cậu thêm nhiều chìa khóa để giải mã những bí ẩn phía trước.</t>
         </is>
       </c>
     </row>
@@ -30992,7 +30992,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Lingyang nhờ cậu giữ bí mật về bản tính thú của cậu. Sau khi nghe về nỗ lực của cậu, Bối Cơ đã mở lòng chia sẻ về mâu thuẫn với Bối Thạch và bày tỏ cảm xúc thật của mình.</t>
+          <t>Linh Dương nhờ cậu giữ bí mật về bản tính thú của cậu. Sau khi nghe về nỗ lực của cậu, Bối Cơ đã mở lòng chia sẻ về mâu thuẫn với Bối Thạch và bày tỏ cảm xúc thật của mình.</t>
         </is>
       </c>
     </row>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>The Séance Society dụ dỗ người ta bằng lời hứa đưa người thân đã khuất trở về. Nhưng tất cả chỉ là trò lừa đảo… Cậu đã tận mắt chứng kiến sự thật đằng sau cái gọi là "hồi sinh" của chúng rồi đấy.</t>
+          <t>Hội Thông Linh dụ dỗ người ta bằng lời hứa đưa người thân đã khuất trở về. Nhưng tất cả chỉ là trò lừa đảo… Cậu đã tận mắt chứng kiến sự thật đằng sau cái gọi là "hồi sinh" của chúng rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -31187,7 +31187,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Yinlin giải thích rằng Hội Séance đứng sau những vụ mất tích gần đây ở Jinzhou. Họ cung cấp những con rối sống động thay thế người thân đã mất, và nhiều người tuyệt vọng đã gia nhập Hội vì lý do này. Tuy nhiên, tương tác thường xuyên với những con rối này làm tăng đáng kể nguy cơ Quá Tải. Yinlin đang lần theo dấu vết của những kẻ chủ mưu và mời cậu gặp cô ngoài thành nếu muốn tìm hiểu thêm về vụ án.</t>
+          <t>Ân Lâm giải thích rằng Hội Séance đứng sau những vụ mất tích gần đây ở Jinzhou. Họ cung cấp những con rối sống động thay thế người thân đã mất, và nhiều người tuyệt vọng đã gia nhập Hội vì lý do này. Tuy nhiên, tương tác thường xuyên với những con rối này làm tăng đáng kể nguy cơ Quá Tải. Ân Lâm đang lần theo dấu vết của những kẻ chủ mưu và mời cậu gặp cô ngoài thành nếu muốn tìm hiểu thêm về vụ án.</t>
         </is>
       </c>
     </row>
@@ -31642,7 +31642,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Wu Sheng nói với cậu rằng ngay cả những thầy thuốc giỏi nhất cũng không thể cứu được tất cả mọi người, giống như ông đã không thể cứu được vợ mình. Những con rối của Người Thợ Làm Búp Bê đã cho họ một cơ hội thứ hai, điều mà không vị bác sĩ nào có thể làm được. Dù Wu Sheng hiểu rõ sự nguy hiểm của những con rối, ông cũng biết chúng có ý nghĩa như thế nào với mọi người ở đây.</t>
+          <t>Ngộ Sinh nói với cậu rằng ngay cả những thầy thuốc giỏi nhất cũng không thể cứu được tất cả mọi người, giống như ông đã không thể cứu được vợ mình. Những con rối của Người Thợ Làm Búp Bê đã cho họ một cơ hội thứ hai, điều mà không vị bác sĩ nào có thể làm được. Dù Ngộ Sinh hiểu rõ sự nguy hiểm của những con rối, ông cũng biết chúng có ý nghĩa như thế nào với mọi người ở đây.</t>
         </is>
       </c>
     </row>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Anyway... Tớ vẫn sẽ giữ chúng an toàn. Chị Yinlin bảo sẽ vứt hết mọi thứ ở đây đi, nhưng tớ tin chúng vẫn còn ý nghĩa với chị ấy và Master Dollmaker.</t>
+          <t>Dù sao... Tớ vẫn sẽ giữ chúng an toàn. Chị Yinlin bảo sẽ vứt hết mọi thứ ở đây đi, nhưng tớ tin chúng vẫn còn ý nghĩa với chị ấy và Sư phụ Dollmaker.</t>
         </is>
       </c>
     </row>
